--- a/artfynd/A 62177-2025 artfynd.xlsx
+++ b/artfynd/A 62177-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130822169</v>
       </c>
       <c r="B2" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>130822196</v>
       </c>
       <c r="B3" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>130822184</v>
       </c>
       <c r="B4" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130822173</v>
+        <v>130822205</v>
       </c>
       <c r="B5" t="n">
-        <v>91795</v>
+        <v>79221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,26 +1083,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>426315</v>
+        <v>426550</v>
       </c>
       <c r="R5" t="n">
-        <v>7048136</v>
+        <v>7048085</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1148,11 +1148,6 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar intill andra vedsvampar i en ca 5 meters granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1180,12 +1175,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,10 +1198,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130822205</v>
+        <v>130822200</v>
       </c>
       <c r="B6" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,10 +1236,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>426550</v>
+        <v>426537</v>
       </c>
       <c r="R6" t="n">
-        <v>7048085</v>
+        <v>7048133</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1329,10 +1324,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130822200</v>
+        <v>130822207</v>
       </c>
       <c r="B7" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1358,19 +1353,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupsjön Öst, Jmt</t>
+          <t>Djupsjön ö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426537</v>
+        <v>426504</v>
       </c>
       <c r="R7" t="n">
-        <v>7048133</v>
+        <v>7047832</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1405,60 +1397,39 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Måttligt</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130822207</v>
+        <v>130822198</v>
       </c>
       <c r="B8" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1484,16 +1455,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Djupsjön ö, Jmt</t>
+          <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426504</v>
+        <v>426516</v>
       </c>
       <c r="R8" t="n">
-        <v>7047832</v>
+        <v>7048217</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1528,39 +1502,60 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Måttligt</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130822198</v>
+        <v>130822181</v>
       </c>
       <c r="B9" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,10 +1590,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>426516</v>
+        <v>426379</v>
       </c>
       <c r="R9" t="n">
-        <v>7048217</v>
+        <v>7048092</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1631,6 +1626,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130822181</v>
+        <v>130822173</v>
       </c>
       <c r="B10" t="n">
-        <v>79220</v>
+        <v>91796</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,26 +1694,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>426379</v>
+        <v>426315</v>
       </c>
       <c r="R10" t="n">
-        <v>7048092</v>
+        <v>7048136</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Flera fruktkroppar intill andra vedsvampar i en ca 5 meters granhögstubbe.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1817,7 +1817,7 @@
         <v>130822189</v>
       </c>
       <c r="B11" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1916,10 +1916,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130822185</v>
+        <v>130822202</v>
       </c>
       <c r="B12" t="n">
-        <v>57863</v>
+        <v>91772</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,21 +1927,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>426407</v>
+        <v>426393</v>
       </c>
       <c r="R12" t="n">
-        <v>7048162</v>
+        <v>7048149</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1987,11 +1987,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 2,5 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2021,7 +2016,7 @@
         <v>130822204</v>
       </c>
       <c r="B13" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2114,7 +2109,7 @@
         <v>130822177</v>
       </c>
       <c r="B14" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2242,10 +2237,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130822187</v>
+        <v>130822199</v>
       </c>
       <c r="B15" t="n">
-        <v>57863</v>
+        <v>91772</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,42 +2248,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupsjön ö, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426288</v>
+        <v>426404</v>
       </c>
       <c r="R15" t="n">
-        <v>7048140</v>
+        <v>7047955</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2321,11 +2308,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Gammalt bohå, högst sannolikt av tretåig hackspett, ca 3 m upp i grantickerötad gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2352,10 +2334,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130822202</v>
+        <v>130822203</v>
       </c>
       <c r="B16" t="n">
-        <v>91771</v>
+        <v>91796</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,23 +2345,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2387,10 +2365,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>426393</v>
+        <v>426286</v>
       </c>
       <c r="R16" t="n">
-        <v>7048149</v>
+        <v>7048138</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2449,10 +2427,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130822199</v>
+        <v>130822175</v>
       </c>
       <c r="B17" t="n">
-        <v>91771</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2460,34 +2438,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupsjön ö, Jmt</t>
+          <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>426404</v>
+        <v>426484</v>
       </c>
       <c r="R17" t="n">
-        <v>7047955</v>
+        <v>7048011</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2522,6 +2500,11 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Relativt rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2534,22 +2517,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130822203</v>
+        <v>130822188</v>
       </c>
       <c r="B18" t="n">
-        <v>91795</v>
+        <v>79221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,30 +2540,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Djupsjön ö, Jmt</t>
+          <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>426286</v>
+        <v>426252</v>
       </c>
       <c r="R18" t="n">
-        <v>7048138</v>
+        <v>7048037</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2615,34 +2605,65 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130822175</v>
+        <v>130822193</v>
       </c>
       <c r="B19" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2668,16 +2689,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426484</v>
+        <v>426296</v>
       </c>
       <c r="R19" t="n">
-        <v>7048011</v>
+        <v>7048165</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2714,7 +2738,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Relativt rikligt på flera granar.</t>
+          <t>Enstaka bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2723,8 +2747,34 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2741,10 +2791,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130822188</v>
+        <v>130822186</v>
       </c>
       <c r="B20" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2779,10 +2829,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426252</v>
+        <v>426225</v>
       </c>
       <c r="R20" t="n">
-        <v>7048037</v>
+        <v>7048007</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,11 +2865,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2872,10 +2917,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130822193</v>
+        <v>130822171</v>
       </c>
       <c r="B21" t="n">
-        <v>79220</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,37 +2928,50 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426296</v>
+        <v>426332</v>
       </c>
       <c r="R21" t="n">
-        <v>7048165</v>
+        <v>7048266</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2950,7 +3008,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Enstaka bålar på flera granar.</t>
+          <t>Synobservation av minst 2 talltitor, möjligen fler. Fyndplatsen finns i flerskiktad äldre granskog med björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2959,33 +3017,12 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3003,10 +3040,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130822186</v>
+        <v>130822201</v>
       </c>
       <c r="B22" t="n">
-        <v>79220</v>
+        <v>91772</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3014,37 +3051,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Djupsjön Öst, Jmt</t>
+          <t>Djupsjön ö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426225</v>
+        <v>426234</v>
       </c>
       <c r="R22" t="n">
-        <v>7048007</v>
+        <v>7048040</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3085,54 +3119,28 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130822171</v>
+        <v>130822255</v>
       </c>
       <c r="B23" t="n">
-        <v>58022</v>
+        <v>91776</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,50 +3148,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426332</v>
+        <v>426447</v>
       </c>
       <c r="R23" t="n">
-        <v>7048266</v>
+        <v>7048182</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3218,23 +3217,39 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Synobservation av minst 2 talltitor, möjligen fler. Fyndplatsen finns i flerskiktad äldre granskog med björkhögstubbar.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3252,10 +3267,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130822201</v>
+        <v>130822179</v>
       </c>
       <c r="B24" t="n">
-        <v>91771</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,34 +3278,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Djupsjön ö, Jmt</t>
+          <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426234</v>
+        <v>426474</v>
       </c>
       <c r="R24" t="n">
-        <v>7048040</v>
+        <v>7048132</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3325,34 +3343,65 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130822179</v>
+        <v>130822190</v>
       </c>
       <c r="B25" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3387,10 +3436,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>426474</v>
+        <v>426298</v>
       </c>
       <c r="R25" t="n">
-        <v>7048132</v>
+        <v>7048081</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3423,11 +3472,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3480,10 +3524,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130822255</v>
+        <v>130822185</v>
       </c>
       <c r="B26" t="n">
-        <v>91775</v>
+        <v>57864</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,41 +3535,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Djupsjön Öst, Jmt</t>
+          <t>Djupsjön ö, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>426447</v>
+        <v>426407</v>
       </c>
       <c r="R26" t="n">
-        <v>7048182</v>
+        <v>7048162</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3560,60 +3605,39 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ca 2,5 m upp i grantickerötad gran</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130822190</v>
+        <v>130822187</v>
       </c>
       <c r="B27" t="n">
-        <v>79220</v>
+        <v>57864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3621,37 +3645,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Djupsjön Öst, Jmt</t>
+          <t>Djupsjön ö, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>426298</v>
+        <v>426288</v>
       </c>
       <c r="R27" t="n">
-        <v>7048081</v>
+        <v>7048140</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3686,50 +3715,29 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Gammalt bohål, högst sannolikt av tretåig hackspett, ca 3 m upp i grantickerötad gran.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>

--- a/artfynd/A 62177-2025 artfynd.xlsx
+++ b/artfynd/A 62177-2025 artfynd.xlsx
@@ -1072,10 +1072,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130822205</v>
+        <v>130822173</v>
       </c>
       <c r="B5" t="n">
-        <v>79221</v>
+        <v>91796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,26 +1083,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1110,10 +1110,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>426550</v>
+        <v>426315</v>
       </c>
       <c r="R5" t="n">
-        <v>7048085</v>
+        <v>7048136</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1148,6 +1148,11 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar intill andra vedsvampar i en ca 5 meters granhögstubbe.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1175,12 +1180,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1198,7 +1203,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130822200</v>
+        <v>130822205</v>
       </c>
       <c r="B6" t="n">
         <v>79221</v>
@@ -1236,10 +1241,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>426537</v>
+        <v>426550</v>
       </c>
       <c r="R6" t="n">
-        <v>7048133</v>
+        <v>7048085</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1324,7 +1329,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130822207</v>
+        <v>130822200</v>
       </c>
       <c r="B7" t="n">
         <v>79221</v>
@@ -1353,16 +1358,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupsjön ö, Jmt</t>
+          <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426504</v>
+        <v>426537</v>
       </c>
       <c r="R7" t="n">
-        <v>7047832</v>
+        <v>7048133</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1397,36 +1405,57 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Måttligt</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130822198</v>
+        <v>130822207</v>
       </c>
       <c r="B8" t="n">
         <v>79221</v>
@@ -1455,19 +1484,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Djupsjön Öst, Jmt</t>
+          <t>Djupsjön ö, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426516</v>
+        <v>426504</v>
       </c>
       <c r="R8" t="n">
-        <v>7048217</v>
+        <v>7047832</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1502,57 +1528,36 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Måttligt</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130822181</v>
+        <v>130822198</v>
       </c>
       <c r="B9" t="n">
         <v>79221</v>
@@ -1590,10 +1595,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>426379</v>
+        <v>426516</v>
       </c>
       <c r="R9" t="n">
-        <v>7048092</v>
+        <v>7048217</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1626,11 +1631,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130822173</v>
+        <v>130822181</v>
       </c>
       <c r="B10" t="n">
-        <v>91796</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,26 +1694,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>426315</v>
+        <v>426379</v>
       </c>
       <c r="R10" t="n">
-        <v>7048136</v>
+        <v>7048092</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar intill andra vedsvampar i en ca 5 meters granhögstubbe.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1916,10 +1916,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130822202</v>
+        <v>130822204</v>
       </c>
       <c r="B12" t="n">
-        <v>91772</v>
+        <v>91796</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,23 +1927,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1951,10 +1947,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>426393</v>
+        <v>426409</v>
       </c>
       <c r="R12" t="n">
-        <v>7048149</v>
+        <v>7048165</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2013,10 +2009,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130822204</v>
+        <v>130822177</v>
       </c>
       <c r="B13" t="n">
-        <v>91796</v>
+        <v>79221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,30 +2020,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Djupsjön ö, Jmt</t>
+          <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>426409</v>
+        <v>426500</v>
       </c>
       <c r="R13" t="n">
-        <v>7048165</v>
+        <v>7048040</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2082,34 +2085,65 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130822177</v>
+        <v>130822202</v>
       </c>
       <c r="B14" t="n">
-        <v>79221</v>
+        <v>91772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,37 +2151,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Djupsjön Öst, Jmt</t>
+          <t>Djupsjön ö, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>426500</v>
+        <v>426393</v>
       </c>
       <c r="R14" t="n">
-        <v>7048040</v>
+        <v>7048149</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2182,65 +2213,34 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130822199</v>
+        <v>130822203</v>
       </c>
       <c r="B15" t="n">
-        <v>91772</v>
+        <v>91796</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,23 +2248,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2272,10 +2268,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426404</v>
+        <v>426286</v>
       </c>
       <c r="R15" t="n">
-        <v>7047955</v>
+        <v>7048138</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2334,10 +2330,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130822203</v>
+        <v>130822175</v>
       </c>
       <c r="B16" t="n">
-        <v>91796</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,30 +2341,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupsjön ö, Jmt</t>
+          <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>426286</v>
+        <v>426484</v>
       </c>
       <c r="R16" t="n">
-        <v>7048138</v>
+        <v>7048011</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2403,6 +2403,11 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Relativt rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2415,22 +2420,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130822175</v>
+        <v>130822199</v>
       </c>
       <c r="B17" t="n">
-        <v>79221</v>
+        <v>91772</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2438,34 +2443,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupsjön Öst, Jmt</t>
+          <t>Djupsjön ö, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>426484</v>
+        <v>426404</v>
       </c>
       <c r="R17" t="n">
-        <v>7048011</v>
+        <v>7047955</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2500,11 +2505,6 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Relativt rikligt på flera granar.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2517,12 +2517,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3137,10 +3137,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130822255</v>
+        <v>130822179</v>
       </c>
       <c r="B23" t="n">
-        <v>91776</v>
+        <v>79221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,30 +3148,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3179,10 +3175,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426447</v>
+        <v>426474</v>
       </c>
       <c r="R23" t="n">
-        <v>7048182</v>
+        <v>7048132</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3217,6 +3213,11 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3244,12 +3245,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3267,10 +3268,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130822179</v>
+        <v>130822255</v>
       </c>
       <c r="B24" t="n">
-        <v>79221</v>
+        <v>91776</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,26 +3279,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3305,10 +3310,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426474</v>
+        <v>426447</v>
       </c>
       <c r="R24" t="n">
-        <v>7048132</v>
+        <v>7048182</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3343,11 +3348,6 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3375,12 +3375,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>

--- a/artfynd/A 62177-2025 artfynd.xlsx
+++ b/artfynd/A 62177-2025 artfynd.xlsx
@@ -1916,10 +1916,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130822204</v>
+        <v>130822177</v>
       </c>
       <c r="B12" t="n">
-        <v>91796</v>
+        <v>79221</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,30 +1927,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupsjön ö, Jmt</t>
+          <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>426409</v>
+        <v>426500</v>
       </c>
       <c r="R12" t="n">
-        <v>7048165</v>
+        <v>7048040</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1985,34 +1992,65 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130822177</v>
+        <v>130822202</v>
       </c>
       <c r="B13" t="n">
-        <v>79221</v>
+        <v>91772</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2020,37 +2058,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Djupsjön Öst, Jmt</t>
+          <t>Djupsjön ö, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>426500</v>
+        <v>426393</v>
       </c>
       <c r="R13" t="n">
-        <v>7048040</v>
+        <v>7048149</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2085,65 +2120,34 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130822202</v>
+        <v>130822204</v>
       </c>
       <c r="B14" t="n">
-        <v>91772</v>
+        <v>91796</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,23 +2155,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>426393</v>
+        <v>426409</v>
       </c>
       <c r="R14" t="n">
-        <v>7048149</v>
+        <v>7048165</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130822203</v>
+        <v>130822175</v>
       </c>
       <c r="B15" t="n">
-        <v>91796</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2248,30 +2248,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Djupsjön ö, Jmt</t>
+          <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426286</v>
+        <v>426484</v>
       </c>
       <c r="R15" t="n">
-        <v>7048138</v>
+        <v>7048011</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2306,6 +2310,11 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Relativt rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2318,22 +2327,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130822175</v>
+        <v>130822199</v>
       </c>
       <c r="B16" t="n">
-        <v>79221</v>
+        <v>91772</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,34 +2350,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupsjön Öst, Jmt</t>
+          <t>Djupsjön ö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>426484</v>
+        <v>426404</v>
       </c>
       <c r="R16" t="n">
-        <v>7048011</v>
+        <v>7047955</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2403,11 +2412,6 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Relativt rikligt på flera granar.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2420,22 +2424,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130822199</v>
+        <v>130822203</v>
       </c>
       <c r="B17" t="n">
-        <v>91772</v>
+        <v>91796</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2443,23 +2447,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>426404</v>
+        <v>426286</v>
       </c>
       <c r="R17" t="n">
-        <v>7047955</v>
+        <v>7048138</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 62177-2025 artfynd.xlsx
+++ b/artfynd/A 62177-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130822169</v>
+        <v>130822199</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Djupsjön Öst, Jmt</t>
+          <t>Djupsjön ö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>426384</v>
+        <v>426404</v>
       </c>
       <c r="R2" t="n">
-        <v>7048087</v>
+        <v>7047955</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +748,6 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran med garnlav.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -769,51 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130822196</v>
+        <v>130822201</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,37 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djupsjön Öst, Jmt</t>
+          <t>Djupsjön ö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>426298</v>
+        <v>426234</v>
       </c>
       <c r="R3" t="n">
-        <v>7048266</v>
+        <v>7048040</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,65 +845,34 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Enstaka på gran.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130822184</v>
+        <v>130822202</v>
       </c>
       <c r="B4" t="n">
-        <v>79244</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,37 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djupsjön Öst, Jmt</t>
+          <t>Djupsjön ö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>426309</v>
+        <v>426393</v>
       </c>
       <c r="R4" t="n">
-        <v>7048040</v>
+        <v>7048149</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,65 +942,34 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130822173</v>
+        <v>130822255</v>
       </c>
       <c r="B5" t="n">
-        <v>91829</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,19 +977,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
@@ -1110,10 +1008,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>426315</v>
+        <v>426447</v>
       </c>
       <c r="R5" t="n">
-        <v>7048136</v>
+        <v>7048182</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1148,11 +1046,6 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar intill andra vedsvampar i en ca 5 meters granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1180,12 +1073,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1203,14 +1096,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130822205</v>
+        <v>130822175</v>
       </c>
       <c r="B6" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1232,19 +1125,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>426550</v>
+        <v>426484</v>
       </c>
       <c r="R6" t="n">
-        <v>7048085</v>
+        <v>7048011</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,40 +1169,19 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Relativt rikligt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1329,14 +1198,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130822200</v>
+        <v>130822177</v>
       </c>
       <c r="B7" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1367,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>426537</v>
+        <v>426500</v>
       </c>
       <c r="R7" t="n">
-        <v>7048133</v>
+        <v>7048040</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1403,6 +1272,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1455,14 +1329,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130822207</v>
+        <v>130822179</v>
       </c>
       <c r="B8" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1484,16 +1358,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Djupsjön ö, Jmt</t>
+          <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>426504</v>
+        <v>426474</v>
       </c>
       <c r="R8" t="n">
-        <v>7047832</v>
+        <v>7048132</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1530,7 +1407,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Måttligt</t>
+          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1539,32 +1416,58 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130822198</v>
+        <v>130822181</v>
       </c>
       <c r="B9" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1595,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>426516</v>
+        <v>426379</v>
       </c>
       <c r="R9" t="n">
-        <v>7048217</v>
+        <v>7048092</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1631,6 +1534,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1683,14 +1591,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130822181</v>
+        <v>130822184</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1721,10 +1629,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>426379</v>
+        <v>426309</v>
       </c>
       <c r="R10" t="n">
-        <v>7048092</v>
+        <v>7048040</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1814,45 +1722,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130822189</v>
+        <v>130822186</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupsjön ö, Jmt</t>
+          <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>426580</v>
+        <v>426225</v>
       </c>
       <c r="R11" t="n">
-        <v>7048241</v>
+        <v>7048007</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1887,70 +1798,98 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130822204</v>
+        <v>130822188</v>
       </c>
       <c r="B12" t="n">
-        <v>91829</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupsjön ö, Jmt</t>
+          <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>426409</v>
+        <v>426252</v>
       </c>
       <c r="R12" t="n">
-        <v>7048165</v>
+        <v>7048037</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1985,38 +1924,69 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130822177</v>
+        <v>130822190</v>
       </c>
       <c r="B13" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2047,10 +2017,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>426500</v>
+        <v>426298</v>
       </c>
       <c r="R13" t="n">
-        <v>7048040</v>
+        <v>7048081</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2083,11 +2053,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2140,45 +2105,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130822202</v>
+        <v>130822193</v>
       </c>
       <c r="B14" t="n">
-        <v>91805</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Djupsjön ö, Jmt</t>
+          <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>426393</v>
+        <v>426296</v>
       </c>
       <c r="R14" t="n">
-        <v>7048149</v>
+        <v>7048165</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2213,69 +2181,103 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130822199</v>
+        <v>130822196</v>
       </c>
       <c r="B15" t="n">
-        <v>91805</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Djupsjön ö, Jmt</t>
+          <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>426404</v>
+        <v>426298</v>
       </c>
       <c r="R15" t="n">
-        <v>7047955</v>
+        <v>7048266</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2310,65 +2312,103 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Enstaka på gran.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130822203</v>
+        <v>130822198</v>
       </c>
       <c r="B16" t="n">
-        <v>91829</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupsjön ö, Jmt</t>
+          <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>426286</v>
+        <v>426516</v>
       </c>
       <c r="R16" t="n">
-        <v>7048138</v>
+        <v>7048217</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2409,32 +2449,58 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130822175</v>
+        <v>130822200</v>
       </c>
       <c r="B17" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2456,16 +2522,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>426484</v>
+        <v>426537</v>
       </c>
       <c r="R17" t="n">
-        <v>7048011</v>
+        <v>7048133</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2500,19 +2569,40 @@
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Relativt rikligt på flera granar.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2529,14 +2619,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130822188</v>
+        <v>130822205</v>
       </c>
       <c r="B18" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2567,10 +2657,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>426252</v>
+        <v>426550</v>
       </c>
       <c r="R18" t="n">
-        <v>7048037</v>
+        <v>7048085</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2603,11 +2693,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2660,14 +2745,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130822193</v>
+        <v>130822207</v>
       </c>
       <c r="B19" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2689,19 +2774,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Djupsjön Öst, Jmt</t>
+          <t>Djupsjön ö, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>426296</v>
+        <v>426504</v>
       </c>
       <c r="R19" t="n">
-        <v>7048165</v>
+        <v>7047832</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2738,7 +2820,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Enstaka bålar på flera granar.</t>
+          <t>Måttligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2747,54 +2829,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130822186</v>
+        <v>130822169</v>
       </c>
       <c r="B20" t="n">
-        <v>79244</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2802,26 +2858,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2829,10 +2890,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>426225</v>
+        <v>426384</v>
       </c>
       <c r="R20" t="n">
-        <v>7048007</v>
+        <v>7048087</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2867,13 +2928,17 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran med garnlav.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2894,12 +2959,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2917,10 +2982,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130822171</v>
+        <v>130822185</v>
       </c>
       <c r="B21" t="n">
-        <v>58043</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,50 +2993,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Djupsjön Öst, Jmt</t>
+          <t>Djupsjön ö, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>426332</v>
+        <v>426407</v>
       </c>
       <c r="R21" t="n">
-        <v>7048266</v>
+        <v>7048162</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3008,7 +3065,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Synobservation av minst 2 talltitor, möjligen fler. Fyndplatsen finns i flerskiktad äldre granskog med björkhögstubbar.</t>
+          <t>Ca 2,5 m upp i grantickerötad gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3019,31 +3076,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130822201</v>
+        <v>130822187</v>
       </c>
       <c r="B22" t="n">
-        <v>91805</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3051,34 +3103,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Djupsjön ö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>426234</v>
+        <v>426288</v>
       </c>
       <c r="R22" t="n">
-        <v>7048040</v>
+        <v>7048140</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3111,6 +3171,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gammalt bohål, högst sannolikt av tretåig hackspett, ca 3 m upp i grantickerötad gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3137,10 +3202,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130822255</v>
+        <v>130822189</v>
       </c>
       <c r="B23" t="n">
-        <v>91809</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,41 +3213,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Djupsjön Öst, Jmt</t>
+          <t>Djupsjön ö, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>426447</v>
+        <v>426580</v>
       </c>
       <c r="R23" t="n">
-        <v>7048182</v>
+        <v>7048241</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3217,60 +3275,39 @@
           <t>2026-01-21</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130822179</v>
+        <v>130822171</v>
       </c>
       <c r="B24" t="n">
-        <v>79244</v>
+        <v>58114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3278,37 +3315,50 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Djupsjön Öst, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>426474</v>
+        <v>426332</v>
       </c>
       <c r="R24" t="n">
-        <v>7048132</v>
+        <v>7048266</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3345,7 +3395,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Enstaka bålar på gran.</t>
+          <t>Synobservation av minst 2 talltitor, möjligen fler. Fyndplatsen finns i flerskiktad äldre granskog med björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3354,33 +3404,12 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3395,352 +3424,6 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>130822190</v>
-      </c>
-      <c r="B25" t="n">
-        <v>79244</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Djupsjön Öst, Jmt</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>426298</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7048081</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>130822185</v>
-      </c>
-      <c r="B26" t="n">
-        <v>57884</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Djupsjön ö, Jmt</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>426407</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7048162</v>
-      </c>
-      <c r="S26" t="n">
-        <v>10</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ca 2,5 m upp i grantickerötad gran</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>130822187</v>
-      </c>
-      <c r="B27" t="n">
-        <v>57884</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Djupsjön ö, Jmt</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>426288</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7048140</v>
-      </c>
-      <c r="S27" t="n">
-        <v>10</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Alsen</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2026-01-21</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Gammalt bohål, högst sannolikt av tretåig hackspett, ca 3 m upp i grantickerötad gran.</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62177-2025 artfynd.xlsx
+++ b/artfynd/A 62177-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822199</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822201</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822202</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1093,6 +1113,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822255</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822175</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822177</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1457,6 +1492,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822179</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1588,6 +1628,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822181</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1719,6 +1764,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822184</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1845,6 +1895,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822186</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1976,6 +2031,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822188</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2102,6 +2162,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822190</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2233,6 +2298,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822193</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2364,6 +2434,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822196</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2490,6 +2565,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822198</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2616,6 +2696,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822200</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2742,6 +2827,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822205</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2844,6 +2934,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822207</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2979,6 +3074,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822169</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3089,6 +3189,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822185</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3199,6 +3304,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822187</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3301,6 +3411,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822189</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3424,8 +3539,38 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130822171</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>